--- a/datasets/xlsx/CSFaceit.xlsx
+++ b/datasets/xlsx/CSFaceit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D764BE-97B2-4619-98E3-52A656244EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA961C9B-3D06-4F9C-B7F9-510596D0B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="7965" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31405,6 +31405,12 @@
         <f t="shared" si="33"/>
         <v>4.1666666666666664E-2</v>
       </c>
+      <c r="U329">
+        <v>1112</v>
+      </c>
+      <c r="V329">
+        <v>4</v>
+      </c>
       <c r="AA329">
         <f t="shared" si="29"/>
         <v>0</v>

--- a/datasets/xlsx/CSFaceit.xlsx
+++ b/datasets/xlsx/CSFaceit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA961C9B-3D06-4F9C-B7F9-510596D0B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D773C3-56D5-4F5C-A50A-05ED87254ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="7965" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -244,7 +244,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
@@ -584,6 +584,15 @@
   <si>
     <t>StandardTime</t>
   </si>
+  <si>
+    <t>Placement</t>
+  </si>
+  <si>
+    <t>06 May 2026</t>
+  </si>
+  <si>
+    <t>Haven't played FaceIt in too long. We got Overpass and Anubis back in the pool, plus Cache as a bonus. Season 8 also started a bit ago, so Placement matches for that.</t>
+  </si>
 </sst>
 </file>
 
@@ -618,13 +627,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -992,6 +1005,7 @@
     <col min="6" max="6" width="12.140625" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" customWidth="1"/>
     <col min="25" max="25" width="12" customWidth="1"/>
     <col min="26" max="26" width="10.85546875" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" customWidth="1"/>
@@ -31399,14 +31413,65 @@
       </c>
     </row>
     <row r="329" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="B329" s="1"/>
-      <c r="C329" s="2"/>
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329" s="1">
+        <v>46148</v>
+      </c>
+      <c r="C329" s="2">
+        <v>2.8472222222222222E-2</v>
+      </c>
       <c r="D329" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="U329">
-        <v>1112</v>
+        <v>2.8472222222222222E-2</v>
+      </c>
+      <c r="E329" t="s">
+        <v>53</v>
+      </c>
+      <c r="F329" t="s">
+        <v>106</v>
+      </c>
+      <c r="G329" t="s">
+        <v>83</v>
+      </c>
+      <c r="H329" t="s">
+        <v>56</v>
+      </c>
+      <c r="I329" t="s">
+        <v>81</v>
+      </c>
+      <c r="J329" t="s">
+        <v>63</v>
+      </c>
+      <c r="K329">
+        <v>6</v>
+      </c>
+      <c r="L329">
+        <v>3</v>
+      </c>
+      <c r="M329">
+        <v>10</v>
+      </c>
+      <c r="N329">
+        <v>5</v>
+      </c>
+      <c r="O329">
+        <v>3</v>
+      </c>
+      <c r="P329">
+        <v>12</v>
+      </c>
+      <c r="R329">
+        <v>41</v>
+      </c>
+      <c r="S329">
+        <v>18</v>
+      </c>
+      <c r="T329" t="s">
+        <v>65</v>
+      </c>
+      <c r="U329" t="s">
+        <v>113</v>
       </c>
       <c r="V329">
         <v>4</v>
@@ -31425,21 +31490,18 @@
       </c>
       <c r="AE329">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D330" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D330" s="2"/>
       <c r="AA330">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC330">
         <f t="shared" si="30"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD330">
         <f t="shared" si="31"/>
@@ -31451,17 +31513,14 @@
       </c>
     </row>
     <row r="331" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D331" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D331" s="2"/>
       <c r="AA331">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC331">
         <f t="shared" si="30"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD331">
         <f t="shared" si="31"/>
@@ -31473,17 +31532,14 @@
       </c>
     </row>
     <row r="332" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D332" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D332" s="2"/>
       <c r="AA332">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC332">
         <f t="shared" si="30"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD332">
         <f t="shared" si="31"/>
@@ -31495,17 +31551,14 @@
       </c>
     </row>
     <row r="333" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D333" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D333" s="2"/>
       <c r="AA333">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC333">
         <f t="shared" si="30"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD333">
         <f t="shared" si="31"/>
@@ -31517,17 +31570,14 @@
       </c>
     </row>
     <row r="334" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D334" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D334" s="2"/>
       <c r="AA334">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC334">
         <f t="shared" si="30"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD334">
         <f t="shared" si="31"/>
@@ -31539,17 +31589,14 @@
       </c>
     </row>
     <row r="335" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D335" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D335" s="2"/>
       <c r="AA335">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC335">
         <f t="shared" si="30"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD335">
         <f t="shared" si="31"/>
@@ -31561,17 +31608,14 @@
       </c>
     </row>
     <row r="336" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D336" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D336" s="2"/>
       <c r="AA336">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC336">
         <f t="shared" si="30"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD336">
         <f t="shared" si="31"/>
@@ -31583,17 +31627,14 @@
       </c>
     </row>
     <row r="337" spans="4:31" x14ac:dyDescent="0.25">
-      <c r="D337" s="2">
-        <f t="shared" si="33"/>
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="D337" s="2"/>
       <c r="AA337">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AC337">
         <f t="shared" si="30"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD337">
         <f t="shared" si="31"/>
@@ -31619,7 +31660,7 @@
     <col min="2" max="2" width="59.42578125" customWidth="1"/>
     <col min="5" max="5" width="23.140625" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="38.42578125" customWidth="1"/>
+    <col min="8" max="8" width="54.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -31709,6 +31750,12 @@
       <c r="E5" t="s">
         <v>77</v>
       </c>
+      <c r="G5" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -31723,6 +31770,7 @@
       <c r="E6" t="s">
         <v>74</v>
       </c>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -31737,6 +31785,7 @@
       <c r="E7" t="s">
         <v>76</v>
       </c>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -31907,6 +31956,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H5:H7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datasets/xlsx/CSFaceit.xlsx
+++ b/datasets/xlsx/CSFaceit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\CS2 Project\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\avery\OneDrive\Desktop\Programming SHit\HardWareWebsite\datasets\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D773C3-56D5-4F5C-A50A-05ED87254ECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103916BC-7F9A-4919-B90C-221C3DA27004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -244,7 +244,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="116">
   <si>
     <t>ID</t>
   </si>
@@ -634,10 +634,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -31052,7 +31052,7 @@
         <v>0.97986111111111107</v>
       </c>
       <c r="D324" s="2">
-        <f t="shared" ref="D324:D337" si="33">C324 + 1/24</f>
+        <f t="shared" ref="D324:D328" si="33">C324 + 1/24</f>
         <v>1.0215277777777778</v>
       </c>
       <c r="E324" t="s">
@@ -31494,7 +31494,57 @@
       </c>
     </row>
     <row r="330" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="D330" s="2"/>
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330" s="1">
+        <v>46249</v>
+      </c>
+      <c r="C330" s="2">
+        <v>0.95694444444444449</v>
+      </c>
+      <c r="D330" s="2">
+        <v>0.95694444444444449</v>
+      </c>
+      <c r="E330" t="s">
+        <v>53</v>
+      </c>
+      <c r="F330" t="s">
+        <v>107</v>
+      </c>
+      <c r="G330" t="s">
+        <v>83</v>
+      </c>
+      <c r="H330" t="s">
+        <v>65</v>
+      </c>
+      <c r="I330" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q330">
+        <v>1796</v>
+      </c>
+      <c r="R330">
+        <v>94</v>
+      </c>
+      <c r="S330">
+        <v>61</v>
+      </c>
+      <c r="T330" t="s">
+        <v>65</v>
+      </c>
+      <c r="U330" t="s">
+        <v>113</v>
+      </c>
+      <c r="V330">
+        <v>1</v>
+      </c>
+      <c r="W330">
+        <v>1.39</v>
+      </c>
+      <c r="X330">
+        <v>48</v>
+      </c>
       <c r="AA330">
         <f t="shared" si="29"/>
         <v>0</v>
@@ -31509,10 +31559,23 @@
       </c>
       <c r="AE330">
         <f t="shared" si="32"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="AF330">
+        <v>4.04</v>
+      </c>
+      <c r="AG330">
+        <v>32</v>
+      </c>
+      <c r="AH330">
+        <v>81</v>
+      </c>
+      <c r="AI330">
+        <v>55</v>
       </c>
     </row>
     <row r="331" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="B331" s="1"/>
       <c r="D331" s="2"/>
       <c r="AA331">
         <f t="shared" si="29"/>
@@ -31520,7 +31583,7 @@
       </c>
       <c r="AC331">
         <f t="shared" si="30"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD331">
         <f t="shared" si="31"/>
@@ -31539,7 +31602,7 @@
       </c>
       <c r="AC332">
         <f t="shared" si="30"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD332">
         <f t="shared" si="31"/>
@@ -31558,7 +31621,7 @@
       </c>
       <c r="AC333">
         <f t="shared" si="30"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD333">
         <f t="shared" si="31"/>
@@ -31577,7 +31640,7 @@
       </c>
       <c r="AC334">
         <f t="shared" si="30"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD334">
         <f t="shared" si="31"/>
@@ -31596,7 +31659,7 @@
       </c>
       <c r="AC335">
         <f t="shared" si="30"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD335">
         <f t="shared" si="31"/>
@@ -31615,7 +31678,7 @@
       </c>
       <c r="AC336">
         <f t="shared" si="30"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD336">
         <f t="shared" si="31"/>
@@ -31634,7 +31697,7 @@
       </c>
       <c r="AC337">
         <f t="shared" si="30"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD337">
         <f t="shared" si="31"/>
@@ -31753,7 +31816,7 @@
       <c r="G5" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>115</v>
       </c>
     </row>
@@ -31770,7 +31833,7 @@
       <c r="E6" t="s">
         <v>74</v>
       </c>
-      <c r="H6" s="6"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -31785,7 +31848,7 @@
       <c r="E7" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="6"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
